--- a/data/AE-model-mirror.xlsx
+++ b/data/AE-model-mirror.xlsx
@@ -208,7 +208,7 @@
     <t>Fixed cost, USD/yr</t>
   </si>
   <si>
-    <t>Labour, maintenance and overhead. Omitting these gave a 158 USD/t cash cost, about twenty times too low, and made every scenario look profitable.</t>
+    <t>Labour, maintenance and overhead. Omitting these gave a 157.77 USD/t cash cost against the corrected 795.02, a factor of 5.0, and made every scenario look profitable.</t>
   </si>
   <si>
     <t>Freight, USD/yr</t>
